--- a/results/test/multiClass_AD_results.xlsx
+++ b/results/test/multiClass_AD_results.xlsx
@@ -566,49 +566,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.361</v>
+        <v>0.44299</v>
       </c>
       <c r="C2" t="n">
-        <v>0.326</v>
+        <v>0.38921</v>
       </c>
       <c r="D2" t="n">
-        <v>0.403</v>
+        <v>0.51402</v>
       </c>
       <c r="E2" t="n">
-        <v>0.548</v>
+        <v>0.68763</v>
       </c>
       <c r="F2" t="n">
-        <v>0.381</v>
+        <v>0.53395</v>
       </c>
       <c r="G2" t="n">
-        <v>0.972</v>
+        <v>0.96552</v>
       </c>
       <c r="H2" t="n">
-        <v>0.528</v>
+        <v>0.42879</v>
       </c>
       <c r="I2" t="n">
-        <v>0.381</v>
+        <v>0.28591</v>
       </c>
       <c r="J2" t="n">
-        <v>0.857</v>
+        <v>0.85714</v>
       </c>
       <c r="K2" t="n">
-        <v>0.624</v>
+        <v>0.66667</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7</v>
+        <v>0.81818</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5625</v>
       </c>
       <c r="N2" t="n">
-        <v>0.183</v>
+        <v>0.1147</v>
       </c>
       <c r="O2" t="n">
-        <v>0.122</v>
+        <v>0.07049</v>
       </c>
       <c r="P2" t="n">
-        <v>0.361</v>
+        <v>0.30769</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -620,19 +620,19 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.082</v>
+        <v>0.10325</v>
       </c>
       <c r="U2" t="n">
-        <v>0.12</v>
+        <v>0.10673</v>
       </c>
       <c r="V2" t="n">
-        <v>0.062</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4</v>
+        <v>0.41379</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6</v>
+        <v>0.66667</v>
       </c>
       <c r="Y2" t="n">
         <v>0.3</v>
@@ -645,31 +645,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.378</v>
+        <v>0.47075</v>
       </c>
       <c r="C3" t="n">
-        <v>0.35</v>
+        <v>0.4217</v>
       </c>
       <c r="D3" t="n">
-        <v>0.41</v>
+        <v>0.53271</v>
       </c>
       <c r="E3" t="n">
-        <v>0.555</v>
+        <v>0.73304</v>
       </c>
       <c r="F3" t="n">
-        <v>0.384</v>
+        <v>0.57859</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.528</v>
+        <v>0.42889</v>
       </c>
       <c r="I3" t="n">
-        <v>0.381</v>
+        <v>0.286</v>
       </c>
       <c r="J3" t="n">
-        <v>0.857</v>
+        <v>0.85714</v>
       </c>
       <c r="K3" t="n">
         <v>0.72</v>
@@ -678,16 +678,16 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5625</v>
       </c>
       <c r="N3" t="n">
-        <v>0.249</v>
+        <v>0.17098</v>
       </c>
       <c r="O3" t="n">
-        <v>0.183</v>
+        <v>0.11353</v>
       </c>
       <c r="P3" t="n">
-        <v>0.389</v>
+        <v>0.34615</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -699,19 +699,19 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.082</v>
+        <v>0.10879</v>
       </c>
       <c r="U3" t="n">
-        <v>0.119</v>
+        <v>0.11926</v>
       </c>
       <c r="V3" t="n">
-        <v>0.062</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4</v>
+        <v>0.41379</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6</v>
+        <v>0.66667</v>
       </c>
       <c r="Y3" t="n">
         <v>0.3</v>
@@ -724,49 +724,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.342</v>
+        <v>0.39583</v>
       </c>
       <c r="C4" t="n">
-        <v>0.351</v>
+        <v>0.38998</v>
       </c>
       <c r="D4" t="n">
-        <v>0.333</v>
+        <v>0.40187</v>
       </c>
       <c r="E4" t="n">
-        <v>0.545</v>
+        <v>0.5356300000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.428</v>
+        <v>0.47108</v>
       </c>
       <c r="G4" t="n">
-        <v>0.75</v>
+        <v>0.62069</v>
       </c>
       <c r="H4" t="n">
-        <v>0.425</v>
+        <v>0.38184</v>
       </c>
       <c r="I4" t="n">
-        <v>0.339</v>
+        <v>0.28671</v>
       </c>
       <c r="J4" t="n">
-        <v>0.571</v>
+        <v>0.57143</v>
       </c>
       <c r="K4" t="n">
-        <v>0.545</v>
+        <v>0.61538</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M4" t="n">
         <v>0.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.231</v>
+        <v>0.19551</v>
       </c>
       <c r="O4" t="n">
-        <v>0.165</v>
+        <v>0.13622</v>
       </c>
       <c r="P4" t="n">
-        <v>0.389</v>
+        <v>0.34615</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.094</v>
+        <v>0.13103</v>
       </c>
       <c r="U4" t="n">
         <v>0.19</v>
       </c>
       <c r="V4" t="n">
-        <v>0.062</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="n">
         <v>0.4</v>
@@ -803,49 +803,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.362</v>
+        <v>0.44994</v>
       </c>
       <c r="C5" t="n">
-        <v>0.376</v>
+        <v>0.47194</v>
       </c>
       <c r="D5" t="n">
-        <v>0.349</v>
+        <v>0.42991</v>
       </c>
       <c r="E5" t="n">
-        <v>0.546</v>
+        <v>0.60056</v>
       </c>
       <c r="F5" t="n">
-        <v>0.413</v>
+        <v>0.55435</v>
       </c>
       <c r="G5" t="n">
-        <v>0.806</v>
+        <v>0.65517</v>
       </c>
       <c r="H5" t="n">
-        <v>0.382</v>
+        <v>0.36323</v>
       </c>
       <c r="I5" t="n">
-        <v>0.287</v>
+        <v>0.26623</v>
       </c>
       <c r="J5" t="n">
-        <v>0.571</v>
+        <v>0.57143</v>
       </c>
       <c r="K5" t="n">
-        <v>0.643</v>
+        <v>0.69498</v>
       </c>
       <c r="L5" t="n">
-        <v>0.75</v>
+        <v>0.90909</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5625</v>
       </c>
       <c r="N5" t="n">
-        <v>0.331</v>
+        <v>0.29435</v>
       </c>
       <c r="O5" t="n">
-        <v>0.275</v>
+        <v>0.2384</v>
       </c>
       <c r="P5" t="n">
-        <v>0.417</v>
+        <v>0.38462</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -857,13 +857,13 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.093</v>
+        <v>0.1184</v>
       </c>
       <c r="U5" t="n">
-        <v>0.181</v>
+        <v>0.1451</v>
       </c>
       <c r="V5" t="n">
-        <v>0.062</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="n">
         <v>0.4</v>
@@ -1023,49 +1023,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.317</v>
+        <v>0.39818</v>
       </c>
       <c r="C2" t="n">
-        <v>0.326</v>
+        <v>0.38921</v>
       </c>
       <c r="D2" t="n">
-        <v>0.307</v>
+        <v>0.40757</v>
       </c>
       <c r="E2" t="n">
-        <v>0.522</v>
+        <v>0.6364</v>
       </c>
       <c r="F2" t="n">
-        <v>0.381</v>
+        <v>0.53395</v>
       </c>
       <c r="G2" t="n">
-        <v>0.83</v>
+        <v>0.7875</v>
       </c>
       <c r="H2" t="n">
-        <v>0.496</v>
+        <v>0.40781</v>
       </c>
       <c r="I2" t="n">
-        <v>0.381</v>
+        <v>0.28591</v>
       </c>
       <c r="J2" t="n">
-        <v>0.711</v>
+        <v>0.71095</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.59105</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7</v>
+        <v>0.81818</v>
       </c>
       <c r="M2" t="n">
-        <v>0.463</v>
+        <v>0.46262</v>
       </c>
       <c r="N2" t="n">
-        <v>0.172</v>
+        <v>0.1106</v>
       </c>
       <c r="O2" t="n">
-        <v>0.122</v>
+        <v>0.07049</v>
       </c>
       <c r="P2" t="n">
-        <v>0.291</v>
+        <v>0.25665</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1077,22 +1077,22 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.045</v>
+        <v>0.06202</v>
       </c>
       <c r="U2" t="n">
-        <v>0.12</v>
+        <v>0.10673</v>
       </c>
       <c r="V2" t="n">
-        <v>0.027</v>
+        <v>0.04371</v>
       </c>
       <c r="W2" t="n">
-        <v>0.212</v>
+        <v>0.21531</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6</v>
+        <v>0.66667</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.128</v>
+        <v>0.12839</v>
       </c>
     </row>
     <row r="3">
@@ -1102,49 +1102,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.327</v>
+        <v>0.41448</v>
       </c>
       <c r="C3" t="n">
-        <v>0.35</v>
+        <v>0.4217</v>
       </c>
       <c r="D3" t="n">
-        <v>0.307</v>
+        <v>0.4075</v>
       </c>
       <c r="E3" t="n">
-        <v>0.525</v>
+        <v>0.66565</v>
       </c>
       <c r="F3" t="n">
-        <v>0.384</v>
+        <v>0.57859</v>
       </c>
       <c r="G3" t="n">
-        <v>0.826</v>
+        <v>0.78355</v>
       </c>
       <c r="H3" t="n">
-        <v>0.495</v>
+        <v>0.407</v>
       </c>
       <c r="I3" t="n">
-        <v>0.381</v>
+        <v>0.286</v>
       </c>
       <c r="J3" t="n">
-        <v>0.705</v>
+        <v>0.70545</v>
       </c>
       <c r="K3" t="n">
-        <v>0.632</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.462</v>
+        <v>0.46156</v>
       </c>
       <c r="N3" t="n">
-        <v>0.225</v>
+        <v>0.15835</v>
       </c>
       <c r="O3" t="n">
-        <v>0.183</v>
+        <v>0.11353</v>
       </c>
       <c r="P3" t="n">
-        <v>0.292</v>
+        <v>0.26169</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1156,22 +1156,22 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.044</v>
+        <v>0.06382</v>
       </c>
       <c r="U3" t="n">
-        <v>0.119</v>
+        <v>0.11926</v>
       </c>
       <c r="V3" t="n">
-        <v>0.027</v>
+        <v>0.04356</v>
       </c>
       <c r="W3" t="n">
-        <v>0.216</v>
+        <v>0.21998</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6</v>
+        <v>0.66667</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.132</v>
+        <v>0.13172</v>
       </c>
     </row>
     <row r="4">
@@ -1181,49 +1181,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.312</v>
+        <v>0.3713</v>
       </c>
       <c r="C4" t="n">
-        <v>0.351</v>
+        <v>0.38998</v>
       </c>
       <c r="D4" t="n">
-        <v>0.282</v>
+        <v>0.35433</v>
       </c>
       <c r="E4" t="n">
-        <v>0.537</v>
+        <v>0.52552</v>
       </c>
       <c r="F4" t="n">
-        <v>0.428</v>
+        <v>0.47108</v>
       </c>
       <c r="G4" t="n">
-        <v>0.718</v>
+        <v>0.59419</v>
       </c>
       <c r="H4" t="n">
-        <v>0.423</v>
+        <v>0.38019</v>
       </c>
       <c r="I4" t="n">
-        <v>0.339</v>
+        <v>0.28671</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.56409</v>
       </c>
       <c r="K4" t="n">
-        <v>0.522</v>
+        <v>0.58622</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0.463</v>
+        <v>0.4626</v>
       </c>
       <c r="N4" t="n">
-        <v>0.216</v>
+        <v>0.185</v>
       </c>
       <c r="O4" t="n">
-        <v>0.165</v>
+        <v>0.13622</v>
       </c>
       <c r="P4" t="n">
-        <v>0.314</v>
+        <v>0.28821</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1235,22 +1235,22 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007</v>
+        <v>0.01105</v>
       </c>
       <c r="U4" t="n">
         <v>0.19</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004</v>
+        <v>0.00569</v>
       </c>
       <c r="W4" t="n">
-        <v>0.275</v>
+        <v>0.27463</v>
       </c>
       <c r="X4" t="n">
         <v>0.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.178</v>
+        <v>0.17806</v>
       </c>
     </row>
     <row r="5">
@@ -1260,49 +1260,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.326</v>
+        <v>0.40867</v>
       </c>
       <c r="C5" t="n">
-        <v>0.376</v>
+        <v>0.47194</v>
       </c>
       <c r="D5" t="n">
-        <v>0.288</v>
+        <v>0.36036</v>
       </c>
       <c r="E5" t="n">
-        <v>0.534</v>
+        <v>0.58164</v>
       </c>
       <c r="F5" t="n">
-        <v>0.413</v>
+        <v>0.55435</v>
       </c>
       <c r="G5" t="n">
-        <v>0.757</v>
+        <v>0.61175</v>
       </c>
       <c r="H5" t="n">
-        <v>0.379</v>
+        <v>0.36098</v>
       </c>
       <c r="I5" t="n">
-        <v>0.287</v>
+        <v>0.26623</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.56042</v>
       </c>
       <c r="K5" t="n">
-        <v>0.574</v>
+        <v>0.61499</v>
       </c>
       <c r="L5" t="n">
-        <v>0.75</v>
+        <v>0.90909</v>
       </c>
       <c r="M5" t="n">
-        <v>0.465</v>
+        <v>0.46466</v>
       </c>
       <c r="N5" t="n">
-        <v>0.292</v>
+        <v>0.26145</v>
       </c>
       <c r="O5" t="n">
-        <v>0.275</v>
+        <v>0.2384</v>
       </c>
       <c r="P5" t="n">
-        <v>0.312</v>
+        <v>0.28943</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1314,22 +1314,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007</v>
+        <v>0.01067</v>
       </c>
       <c r="U5" t="n">
-        <v>0.181</v>
+        <v>0.1451</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003</v>
+        <v>0.00554</v>
       </c>
       <c r="W5" t="n">
-        <v>0.286</v>
+        <v>0.28624</v>
       </c>
       <c r="X5" t="n">
         <v>0.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.188</v>
+        <v>0.18796</v>
       </c>
     </row>
   </sheetData>
@@ -1480,49 +1480,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.297</v>
+        <v>0.37686</v>
       </c>
       <c r="C2" t="n">
-        <v>0.326</v>
+        <v>0.38921</v>
       </c>
       <c r="D2" t="n">
-        <v>0.272</v>
+        <v>0.36526</v>
       </c>
       <c r="E2" t="n">
-        <v>0.512</v>
+        <v>0.61238</v>
       </c>
       <c r="F2" t="n">
-        <v>0.381</v>
+        <v>0.53395</v>
       </c>
       <c r="G2" t="n">
-        <v>0.777</v>
+        <v>0.71782</v>
       </c>
       <c r="H2" t="n">
-        <v>0.474</v>
+        <v>0.39292</v>
       </c>
       <c r="I2" t="n">
-        <v>0.381</v>
+        <v>0.28591</v>
       </c>
       <c r="J2" t="n">
-        <v>0.628</v>
+        <v>0.62797</v>
       </c>
       <c r="K2" t="n">
-        <v>0.527</v>
+        <v>0.55679</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7</v>
+        <v>0.81818</v>
       </c>
       <c r="M2" t="n">
-        <v>0.422</v>
+        <v>0.42198</v>
       </c>
       <c r="N2" t="n">
-        <v>0.159</v>
+        <v>0.10716</v>
       </c>
       <c r="O2" t="n">
-        <v>0.122</v>
+        <v>0.07049</v>
       </c>
       <c r="P2" t="n">
-        <v>0.225</v>
+        <v>0.22336</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1534,22 +1534,22 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.014</v>
+        <v>0.02189</v>
       </c>
       <c r="U2" t="n">
-        <v>0.12</v>
+        <v>0.10673</v>
       </c>
       <c r="V2" t="n">
-        <v>0.008</v>
+        <v>0.0122</v>
       </c>
       <c r="W2" t="n">
-        <v>0.199</v>
+        <v>0.20192</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6</v>
+        <v>0.66667</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.119</v>
+        <v>0.11898</v>
       </c>
     </row>
     <row r="3">
@@ -1559,49 +1559,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.302</v>
+        <v>0.3851</v>
       </c>
       <c r="C3" t="n">
-        <v>0.35</v>
+        <v>0.4217</v>
       </c>
       <c r="D3" t="n">
-        <v>0.266</v>
+        <v>0.35434</v>
       </c>
       <c r="E3" t="n">
-        <v>0.509</v>
+        <v>0.62967</v>
       </c>
       <c r="F3" t="n">
-        <v>0.384</v>
+        <v>0.57859</v>
       </c>
       <c r="G3" t="n">
-        <v>0.752</v>
+        <v>0.69065</v>
       </c>
       <c r="H3" t="n">
-        <v>0.471</v>
+        <v>0.39074</v>
       </c>
       <c r="I3" t="n">
-        <v>0.381</v>
+        <v>0.286</v>
       </c>
       <c r="J3" t="n">
-        <v>0.617</v>
+        <v>0.61653</v>
       </c>
       <c r="K3" t="n">
-        <v>0.579</v>
+        <v>0.5789</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.407</v>
+        <v>0.40736</v>
       </c>
       <c r="N3" t="n">
-        <v>0.199</v>
+        <v>0.15007</v>
       </c>
       <c r="O3" t="n">
-        <v>0.183</v>
+        <v>0.11353</v>
       </c>
       <c r="P3" t="n">
-        <v>0.219</v>
+        <v>0.22133</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.014</v>
+        <v>0.02197</v>
       </c>
       <c r="U3" t="n">
-        <v>0.119</v>
+        <v>0.11926</v>
       </c>
       <c r="V3" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="W3" t="n">
-        <v>0.197</v>
+        <v>0.20003</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6</v>
+        <v>0.66667</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.118</v>
+        <v>0.11767</v>
       </c>
     </row>
     <row r="4">
@@ -1638,49 +1638,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.301</v>
+        <v>0.35861</v>
       </c>
       <c r="C4" t="n">
-        <v>0.351</v>
+        <v>0.38998</v>
       </c>
       <c r="D4" t="n">
-        <v>0.264</v>
+        <v>0.33191</v>
       </c>
       <c r="E4" t="n">
-        <v>0.529</v>
+        <v>0.51684</v>
       </c>
       <c r="F4" t="n">
-        <v>0.428</v>
+        <v>0.47108</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.5724399999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.419</v>
+        <v>0.37694</v>
       </c>
       <c r="I4" t="n">
-        <v>0.339</v>
+        <v>0.28671</v>
       </c>
       <c r="J4" t="n">
-        <v>0.55</v>
+        <v>0.55004</v>
       </c>
       <c r="K4" t="n">
-        <v>0.496</v>
+        <v>0.55266</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0.422</v>
+        <v>0.42214</v>
       </c>
       <c r="N4" t="n">
-        <v>0.197</v>
+        <v>0.17661</v>
       </c>
       <c r="O4" t="n">
-        <v>0.165</v>
+        <v>0.13622</v>
       </c>
       <c r="P4" t="n">
-        <v>0.245</v>
+        <v>0.25103</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1692,22 +1692,22 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.00032</v>
       </c>
       <c r="U4" t="n">
         <v>0.19</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.00016</v>
       </c>
       <c r="W4" t="n">
-        <v>0.275</v>
+        <v>0.27463</v>
       </c>
       <c r="X4" t="n">
         <v>0.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.178</v>
+        <v>0.17806</v>
       </c>
     </row>
     <row r="5">
@@ -1717,49 +1717,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.311</v>
+        <v>0.38783</v>
       </c>
       <c r="C5" t="n">
-        <v>0.376</v>
+        <v>0.47194</v>
       </c>
       <c r="D5" t="n">
-        <v>0.265</v>
+        <v>0.32916</v>
       </c>
       <c r="E5" t="n">
-        <v>0.522</v>
+        <v>0.5631699999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.413</v>
+        <v>0.55435</v>
       </c>
       <c r="G5" t="n">
-        <v>0.71</v>
+        <v>0.57228</v>
       </c>
       <c r="H5" t="n">
-        <v>0.375</v>
+        <v>0.35662</v>
       </c>
       <c r="I5" t="n">
-        <v>0.287</v>
+        <v>0.26623</v>
       </c>
       <c r="J5" t="n">
-        <v>0.54</v>
+        <v>0.53994</v>
       </c>
       <c r="K5" t="n">
-        <v>0.529</v>
+        <v>0.56415</v>
       </c>
       <c r="L5" t="n">
-        <v>0.75</v>
+        <v>0.90909</v>
       </c>
       <c r="M5" t="n">
-        <v>0.409</v>
+        <v>0.40898</v>
       </c>
       <c r="N5" t="n">
-        <v>0.255</v>
+        <v>0.24259</v>
       </c>
       <c r="O5" t="n">
-        <v>0.275</v>
+        <v>0.2384</v>
       </c>
       <c r="P5" t="n">
-        <v>0.238</v>
+        <v>0.24693</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1771,22 +1771,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.00031</v>
       </c>
       <c r="U5" t="n">
-        <v>0.181</v>
+        <v>0.1451</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.00015</v>
       </c>
       <c r="W5" t="n">
-        <v>0.286</v>
+        <v>0.28624</v>
       </c>
       <c r="X5" t="n">
         <v>0.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.188</v>
+        <v>0.18796</v>
       </c>
     </row>
   </sheetData>
@@ -1937,49 +1937,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.29</v>
+        <v>0.37206</v>
       </c>
       <c r="C2" t="n">
-        <v>0.325</v>
+        <v>0.38784</v>
       </c>
       <c r="D2" t="n">
-        <v>0.262</v>
+        <v>0.35752</v>
       </c>
       <c r="E2" t="n">
-        <v>0.509</v>
+        <v>0.60743</v>
       </c>
       <c r="F2" t="n">
-        <v>0.381</v>
+        <v>0.53395</v>
       </c>
       <c r="G2" t="n">
-        <v>0.767</v>
+        <v>0.70438</v>
       </c>
       <c r="H2" t="n">
-        <v>0.474</v>
+        <v>0.39292</v>
       </c>
       <c r="I2" t="n">
-        <v>0.381</v>
+        <v>0.28591</v>
       </c>
       <c r="J2" t="n">
-        <v>0.628</v>
+        <v>0.62797</v>
       </c>
       <c r="K2" t="n">
-        <v>0.527</v>
+        <v>0.55679</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7</v>
+        <v>0.81818</v>
       </c>
       <c r="M2" t="n">
-        <v>0.422</v>
+        <v>0.42198</v>
       </c>
       <c r="N2" t="n">
-        <v>0.153</v>
+        <v>0.10024</v>
       </c>
       <c r="O2" t="n">
-        <v>0.116</v>
+        <v>0.06462</v>
       </c>
       <c r="P2" t="n">
-        <v>0.225</v>
+        <v>0.22336</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1991,22 +1991,22 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.014</v>
+        <v>0.02189</v>
       </c>
       <c r="U2" t="n">
-        <v>0.12</v>
+        <v>0.10673</v>
       </c>
       <c r="V2" t="n">
-        <v>0.008</v>
+        <v>0.0122</v>
       </c>
       <c r="W2" t="n">
-        <v>0.133</v>
+        <v>0.13497</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6</v>
+        <v>0.66667</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.075</v>
+        <v>0.07507999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -2016,49 +2016,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.294</v>
+        <v>0.38004</v>
       </c>
       <c r="C3" t="n">
-        <v>0.346</v>
+        <v>0.41922</v>
       </c>
       <c r="D3" t="n">
-        <v>0.256</v>
+        <v>0.34756</v>
       </c>
       <c r="E3" t="n">
-        <v>0.507</v>
+        <v>0.62646</v>
       </c>
       <c r="F3" t="n">
-        <v>0.384</v>
+        <v>0.57859</v>
       </c>
       <c r="G3" t="n">
-        <v>0.746</v>
+        <v>0.68297</v>
       </c>
       <c r="H3" t="n">
-        <v>0.471</v>
+        <v>0.39074</v>
       </c>
       <c r="I3" t="n">
-        <v>0.381</v>
+        <v>0.286</v>
       </c>
       <c r="J3" t="n">
-        <v>0.617</v>
+        <v>0.61653</v>
       </c>
       <c r="K3" t="n">
-        <v>0.579</v>
+        <v>0.5789</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.407</v>
+        <v>0.40736</v>
       </c>
       <c r="N3" t="n">
-        <v>0.188</v>
+        <v>0.14061</v>
       </c>
       <c r="O3" t="n">
-        <v>0.166</v>
+        <v>0.10369</v>
       </c>
       <c r="P3" t="n">
-        <v>0.217</v>
+        <v>0.21834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -2070,22 +2070,22 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.014</v>
+        <v>0.02197</v>
       </c>
       <c r="U3" t="n">
-        <v>0.119</v>
+        <v>0.11926</v>
       </c>
       <c r="V3" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="W3" t="n">
-        <v>0.134</v>
+        <v>0.13508</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6</v>
+        <v>0.66667</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.075</v>
+        <v>0.07514999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2095,49 +2095,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.301</v>
+        <v>0.35779</v>
       </c>
       <c r="C4" t="n">
-        <v>0.349</v>
+        <v>0.38804</v>
       </c>
       <c r="D4" t="n">
-        <v>0.264</v>
+        <v>0.33191</v>
       </c>
       <c r="E4" t="n">
-        <v>0.529</v>
+        <v>0.51684</v>
       </c>
       <c r="F4" t="n">
-        <v>0.428</v>
+        <v>0.47108</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.5724399999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.419</v>
+        <v>0.37694</v>
       </c>
       <c r="I4" t="n">
-        <v>0.339</v>
+        <v>0.28671</v>
       </c>
       <c r="J4" t="n">
-        <v>0.55</v>
+        <v>0.55004</v>
       </c>
       <c r="K4" t="n">
-        <v>0.496</v>
+        <v>0.55266</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0.422</v>
+        <v>0.42214</v>
       </c>
       <c r="N4" t="n">
-        <v>0.192</v>
+        <v>0.1701</v>
       </c>
       <c r="O4" t="n">
-        <v>0.157</v>
+        <v>0.12864</v>
       </c>
       <c r="P4" t="n">
-        <v>0.245</v>
+        <v>0.25103</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -2149,22 +2149,22 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.00032</v>
       </c>
       <c r="U4" t="n">
         <v>0.19</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.00016</v>
       </c>
       <c r="W4" t="n">
-        <v>0.275</v>
+        <v>0.27463</v>
       </c>
       <c r="X4" t="n">
         <v>0.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.178</v>
+        <v>0.17806</v>
       </c>
     </row>
     <row r="5">
@@ -2174,49 +2174,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.309</v>
+        <v>0.38611</v>
       </c>
       <c r="C5" t="n">
-        <v>0.372</v>
+        <v>0.46733</v>
       </c>
       <c r="D5" t="n">
-        <v>0.265</v>
+        <v>0.32895</v>
       </c>
       <c r="E5" t="n">
-        <v>0.522</v>
+        <v>0.5631699999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.413</v>
+        <v>0.55435</v>
       </c>
       <c r="G5" t="n">
-        <v>0.71</v>
+        <v>0.57228</v>
       </c>
       <c r="H5" t="n">
-        <v>0.375</v>
+        <v>0.35662</v>
       </c>
       <c r="I5" t="n">
-        <v>0.287</v>
+        <v>0.26623</v>
       </c>
       <c r="J5" t="n">
-        <v>0.54</v>
+        <v>0.53994</v>
       </c>
       <c r="K5" t="n">
-        <v>0.528</v>
+        <v>0.5628</v>
       </c>
       <c r="L5" t="n">
-        <v>0.75</v>
+        <v>0.90909</v>
       </c>
       <c r="M5" t="n">
-        <v>0.408</v>
+        <v>0.40755</v>
       </c>
       <c r="N5" t="n">
-        <v>0.247</v>
+        <v>0.22921</v>
       </c>
       <c r="O5" t="n">
-        <v>0.257</v>
+        <v>0.21387</v>
       </c>
       <c r="P5" t="n">
-        <v>0.238</v>
+        <v>0.24693</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2228,22 +2228,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.00031</v>
       </c>
       <c r="U5" t="n">
-        <v>0.181</v>
+        <v>0.1451</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.00015</v>
       </c>
       <c r="W5" t="n">
-        <v>0.286</v>
+        <v>0.28624</v>
       </c>
       <c r="X5" t="n">
         <v>0.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.188</v>
+        <v>0.18796</v>
       </c>
     </row>
   </sheetData>
@@ -2394,49 +2394,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.328</v>
+        <v>0.40923</v>
       </c>
       <c r="C2" t="n">
-        <v>0.326</v>
+        <v>0.38907</v>
       </c>
       <c r="D2" t="n">
-        <v>0.334</v>
+        <v>0.43668</v>
       </c>
       <c r="E2" t="n">
-        <v>0.529</v>
+        <v>0.64919</v>
       </c>
       <c r="F2" t="n">
-        <v>0.87</v>
+        <v>0.83646</v>
       </c>
       <c r="G2" t="n">
-        <v>0.381</v>
+        <v>0.53395</v>
       </c>
       <c r="H2" t="n">
-        <v>0.502</v>
+        <v>0.41173</v>
       </c>
       <c r="I2" t="n">
-        <v>0.745</v>
+        <v>0.74453</v>
       </c>
       <c r="J2" t="n">
-        <v>0.381</v>
+        <v>0.28591</v>
       </c>
       <c r="K2" t="n">
-        <v>0.575</v>
+        <v>0.61102</v>
       </c>
       <c r="L2" t="n">
-        <v>0.49</v>
+        <v>0.49038</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7</v>
+        <v>0.81818</v>
       </c>
       <c r="N2" t="n">
-        <v>0.172</v>
+        <v>0.11052</v>
       </c>
       <c r="O2" t="n">
-        <v>0.299</v>
+        <v>0.26708</v>
       </c>
       <c r="P2" t="n">
-        <v>0.122</v>
+        <v>0.0699</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -2448,22 +2448,22 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.051</v>
+        <v>0.06648</v>
       </c>
       <c r="U2" t="n">
-        <v>0.035</v>
+        <v>0.05677</v>
       </c>
       <c r="V2" t="n">
-        <v>0.12</v>
+        <v>0.10673</v>
       </c>
       <c r="W2" t="n">
-        <v>0.277</v>
+        <v>0.28399</v>
       </c>
       <c r="X2" t="n">
-        <v>0.19</v>
+        <v>0.18982</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6</v>
+        <v>0.66667</v>
       </c>
     </row>
     <row r="3">
@@ -2473,49 +2473,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.339</v>
+        <v>0.42767</v>
       </c>
       <c r="C3" t="n">
-        <v>0.35</v>
+        <v>0.42145</v>
       </c>
       <c r="D3" t="n">
-        <v>0.335</v>
+        <v>0.44096</v>
       </c>
       <c r="E3" t="n">
-        <v>0.532</v>
+        <v>0.68149</v>
       </c>
       <c r="F3" t="n">
-        <v>0.873</v>
+        <v>0.84149</v>
       </c>
       <c r="G3" t="n">
-        <v>0.384</v>
+        <v>0.57859</v>
       </c>
       <c r="H3" t="n">
-        <v>0.501</v>
+        <v>0.41088</v>
       </c>
       <c r="I3" t="n">
-        <v>0.739</v>
+        <v>0.7394500000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.381</v>
+        <v>0.286</v>
       </c>
       <c r="K3" t="n">
-        <v>0.651</v>
+        <v>0.65115</v>
       </c>
       <c r="L3" t="n">
-        <v>0.486</v>
+        <v>0.48568</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.226</v>
+        <v>0.15997</v>
       </c>
       <c r="O3" t="n">
-        <v>0.309</v>
+        <v>0.28307</v>
       </c>
       <c r="P3" t="n">
-        <v>0.181</v>
+        <v>0.11254</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -2527,22 +2527,22 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05</v>
+        <v>0.06925000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.035</v>
+        <v>0.0567</v>
       </c>
       <c r="V3" t="n">
-        <v>0.119</v>
+        <v>0.11926</v>
       </c>
       <c r="W3" t="n">
-        <v>0.278</v>
+        <v>0.28502</v>
       </c>
       <c r="X3" t="n">
-        <v>0.191</v>
+        <v>0.19057</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6</v>
+        <v>0.66667</v>
       </c>
     </row>
     <row r="4">
@@ -2552,49 +2552,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.321</v>
+        <v>0.37722</v>
       </c>
       <c r="C4" t="n">
-        <v>0.35</v>
+        <v>0.38978</v>
       </c>
       <c r="D4" t="n">
-        <v>0.297</v>
+        <v>0.36662</v>
       </c>
       <c r="E4" t="n">
-        <v>0.538</v>
+        <v>0.52696</v>
       </c>
       <c r="F4" t="n">
-        <v>0.723</v>
+        <v>0.59827</v>
       </c>
       <c r="G4" t="n">
-        <v>0.428</v>
+        <v>0.47108</v>
       </c>
       <c r="H4" t="n">
-        <v>0.423</v>
+        <v>0.37987</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.56281</v>
       </c>
       <c r="J4" t="n">
-        <v>0.339</v>
+        <v>0.28671</v>
       </c>
       <c r="K4" t="n">
-        <v>0.524</v>
+        <v>0.58782</v>
       </c>
       <c r="L4" t="n">
-        <v>0.465</v>
+        <v>0.46542</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.216</v>
+        <v>0.18604</v>
       </c>
       <c r="O4" t="n">
-        <v>0.323</v>
+        <v>0.30023</v>
       </c>
       <c r="P4" t="n">
-        <v>0.164</v>
+        <v>0.13547</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -2606,19 +2606,19 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04</v>
+        <v>0.05583</v>
       </c>
       <c r="U4" t="n">
-        <v>0.026</v>
+        <v>0.04176</v>
       </c>
       <c r="V4" t="n">
         <v>0.19</v>
       </c>
       <c r="W4" t="n">
-        <v>0.325</v>
+        <v>0.32478</v>
       </c>
       <c r="X4" t="n">
-        <v>0.227</v>
+        <v>0.22684</v>
       </c>
       <c r="Y4" t="n">
         <v>0.6</v>
@@ -2631,49 +2631,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.336</v>
+        <v>0.41876</v>
       </c>
       <c r="C5" t="n">
-        <v>0.376</v>
+        <v>0.47148</v>
       </c>
       <c r="D5" t="n">
-        <v>0.305</v>
+        <v>0.3788</v>
       </c>
       <c r="E5" t="n">
-        <v>0.535</v>
+        <v>0.58367</v>
       </c>
       <c r="F5" t="n">
-        <v>0.762</v>
+        <v>0.6172800000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.413</v>
+        <v>0.55435</v>
       </c>
       <c r="H5" t="n">
-        <v>0.379</v>
+        <v>0.36058</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.55868</v>
       </c>
       <c r="J5" t="n">
-        <v>0.287</v>
+        <v>0.26623</v>
       </c>
       <c r="K5" t="n">
-        <v>0.588</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.487</v>
+        <v>0.48695</v>
       </c>
       <c r="M5" t="n">
-        <v>0.75</v>
+        <v>0.90909</v>
       </c>
       <c r="N5" t="n">
-        <v>0.296</v>
+        <v>0.26761</v>
       </c>
       <c r="O5" t="n">
-        <v>0.332</v>
+        <v>0.31475</v>
       </c>
       <c r="P5" t="n">
-        <v>0.273</v>
+        <v>0.23595</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2685,19 +2685,19 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.039</v>
+        <v>0.05065</v>
       </c>
       <c r="U5" t="n">
-        <v>0.026</v>
+        <v>0.04171</v>
       </c>
       <c r="V5" t="n">
-        <v>0.181</v>
+        <v>0.1451</v>
       </c>
       <c r="W5" t="n">
-        <v>0.332</v>
+        <v>0.33175</v>
       </c>
       <c r="X5" t="n">
-        <v>0.233</v>
+        <v>0.23277</v>
       </c>
       <c r="Y5" t="n">
         <v>0.6</v>
